--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-ex-biobank-einstellung-blutversorgung.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-ex-biobank-einstellung-blutversorgung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T17:44:24+00:00</t>
+    <t>2026-08-27T17:51:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-ex-biobank-einstellung-blutversorgung.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-ex-biobank-einstellung-blutversorgung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T17:51:13+00:00</t>
+    <t>2026-08-28T06:20:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-ex-biobank-einstellung-blutversorgung.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-ex-biobank-einstellung-blutversorgung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T06:20:20+00:00</t>
+    <t>2026-08-28T06:34:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-ex-biobank-einstellung-blutversorgung.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-ex-biobank-einstellung-blutversorgung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T06:34:01+00:00</t>
+    <t>2026-08-28T06:38:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-ex-biobank-einstellung-blutversorgung.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-ex-biobank-einstellung-blutversorgung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T06:38:44+00:00</t>
+    <t>2026-08-28T07:01:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-ex-biobank-einstellung-blutversorgung.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-ex-biobank-einstellung-blutversorgung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T07:01:07+00:00</t>
+    <t>2026-08-28T07:06:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-ex-biobank-einstellung-blutversorgung.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-ex-biobank-einstellung-blutversorgung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T07:06:33+00:00</t>
+    <t>2026-08-28T07:19:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-ex-biobank-einstellung-blutversorgung.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-ex-biobank-einstellung-blutversorgung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T07:19:00+00:00</t>
+    <t>2026-08-31T13:45:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-ex-biobank-einstellung-blutversorgung.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-ex-biobank-einstellung-blutversorgung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T13:45:53+00:00</t>
+    <t>2026-08-31T14:31:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-ex-biobank-einstellung-blutversorgung.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-ex-biobank-einstellung-blutversorgung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T14:31:15+00:00</t>
+    <t>2026-08-31T14:36:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-ex-biobank-einstellung-blutversorgung.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-ex-biobank-einstellung-blutversorgung.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026.0.1</t>
+    <t>2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T14:36:12+00:00</t>
+    <t>2026-09-02T09:13:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-ex-biobank-einstellung-blutversorgung.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-ex-biobank-einstellung-blutversorgung.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc1</t>
+    <t>2027.0.0-ballot.rc2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T09:13:27+00:00</t>
+    <t>2026-09-02T09:37:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-ex-biobank-einstellung-blutversorgung.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-ex-biobank-einstellung-blutversorgung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T09:37:04+00:00</t>
+    <t>2026-09-02T10:26:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-ex-biobank-einstellung-blutversorgung.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-ex-biobank-einstellung-blutversorgung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T10:26:48+00:00</t>
+    <t>2026-09-02T10:35:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
